--- a/artfynd/A 52294-2020 artfynd.xlsx
+++ b/artfynd/A 52294-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119820554</v>
+        <v>119820560</v>
       </c>
       <c r="B2" t="n">
         <v>97907</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>486159</v>
+        <v>486399</v>
       </c>
       <c r="R2" t="n">
-        <v>6841747</v>
+        <v>6841463</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119820557</v>
+        <v>119820552</v>
       </c>
       <c r="B3" t="n">
         <v>97907</v>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486203</v>
+        <v>486239</v>
       </c>
       <c r="R3" t="n">
-        <v>6841583</v>
+        <v>6841652</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119820559</v>
+        <v>119820554</v>
       </c>
       <c r="B4" t="n">
         <v>97907</v>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486391</v>
+        <v>486159</v>
       </c>
       <c r="R4" t="n">
-        <v>6841482</v>
+        <v>6841747</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119820556</v>
+        <v>119820555</v>
       </c>
       <c r="B5" t="n">
         <v>97907</v>
@@ -1052,13 +1052,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486186</v>
+        <v>486170</v>
       </c>
       <c r="R5" t="n">
-        <v>6841640</v>
+        <v>6841676</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119820560</v>
+        <v>119820559</v>
       </c>
       <c r="B6" t="n">
         <v>97907</v>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486399</v>
+        <v>486391</v>
       </c>
       <c r="R6" t="n">
-        <v>6841463</v>
+        <v>6841482</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119820555</v>
+        <v>119820557</v>
       </c>
       <c r="B7" t="n">
         <v>97907</v>
@@ -1274,13 +1274,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486170</v>
+        <v>486203</v>
       </c>
       <c r="R7" t="n">
-        <v>6841676</v>
+        <v>6841583</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119820552</v>
+        <v>119820556</v>
       </c>
       <c r="B8" t="n">
         <v>97907</v>
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486239</v>
+        <v>486186</v>
       </c>
       <c r="R8" t="n">
-        <v>6841652</v>
+        <v>6841640</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>

--- a/artfynd/A 52294-2020 artfynd.xlsx
+++ b/artfynd/A 52294-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119820560</v>
+        <v>119820557</v>
       </c>
       <c r="B2" t="n">
         <v>97907</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>486399</v>
+        <v>486203</v>
       </c>
       <c r="R2" t="n">
-        <v>6841463</v>
+        <v>6841583</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119820552</v>
+        <v>119820555</v>
       </c>
       <c r="B3" t="n">
         <v>97907</v>
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486239</v>
+        <v>486170</v>
       </c>
       <c r="R3" t="n">
-        <v>6841652</v>
+        <v>6841676</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119820554</v>
+        <v>119820552</v>
       </c>
       <c r="B4" t="n">
         <v>97907</v>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486159</v>
+        <v>486239</v>
       </c>
       <c r="R4" t="n">
-        <v>6841747</v>
+        <v>6841652</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119820555</v>
+        <v>119820559</v>
       </c>
       <c r="B5" t="n">
         <v>97907</v>
@@ -1052,13 +1052,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486170</v>
+        <v>486391</v>
       </c>
       <c r="R5" t="n">
-        <v>6841676</v>
+        <v>6841482</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119820559</v>
+        <v>119820556</v>
       </c>
       <c r="B6" t="n">
         <v>97907</v>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486391</v>
+        <v>486186</v>
       </c>
       <c r="R6" t="n">
-        <v>6841482</v>
+        <v>6841640</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119820557</v>
+        <v>119820560</v>
       </c>
       <c r="B7" t="n">
         <v>97907</v>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486203</v>
+        <v>486399</v>
       </c>
       <c r="R7" t="n">
-        <v>6841583</v>
+        <v>6841463</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1341,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119820556</v>
+        <v>119820554</v>
       </c>
       <c r="B8" t="n">
         <v>97907</v>
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486186</v>
+        <v>486159</v>
       </c>
       <c r="R8" t="n">
-        <v>6841640</v>
+        <v>6841747</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>

--- a/artfynd/A 52294-2020 artfynd.xlsx
+++ b/artfynd/A 52294-2020 artfynd.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119820555</v>
+        <v>119820556</v>
       </c>
       <c r="B3" t="n">
         <v>97907</v>
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486170</v>
+        <v>486186</v>
       </c>
       <c r="R3" t="n">
-        <v>6841676</v>
+        <v>6841640</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119820559</v>
+        <v>119820554</v>
       </c>
       <c r="B5" t="n">
         <v>97907</v>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486391</v>
+        <v>486159</v>
       </c>
       <c r="R5" t="n">
-        <v>6841482</v>
+        <v>6841747</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119820556</v>
+        <v>119820559</v>
       </c>
       <c r="B6" t="n">
         <v>97907</v>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486186</v>
+        <v>486391</v>
       </c>
       <c r="R6" t="n">
-        <v>6841640</v>
+        <v>6841482</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119820560</v>
+        <v>119820555</v>
       </c>
       <c r="B7" t="n">
         <v>97907</v>
@@ -1274,13 +1274,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486399</v>
+        <v>486170</v>
       </c>
       <c r="R7" t="n">
-        <v>6841463</v>
+        <v>6841676</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119820554</v>
+        <v>119820560</v>
       </c>
       <c r="B8" t="n">
         <v>97907</v>
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486159</v>
+        <v>486399</v>
       </c>
       <c r="R8" t="n">
-        <v>6841747</v>
+        <v>6841463</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>

--- a/artfynd/A 52294-2020 artfynd.xlsx
+++ b/artfynd/A 52294-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119820557</v>
+        <v>119820552</v>
       </c>
       <c r="B2" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>486203</v>
+        <v>486239</v>
       </c>
       <c r="R2" t="n">
-        <v>6841583</v>
+        <v>6841652</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -789,7 +789,7 @@
         <v>119820556</v>
       </c>
       <c r="B3" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119820552</v>
+        <v>119820560</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486239</v>
+        <v>486399</v>
       </c>
       <c r="R4" t="n">
-        <v>6841652</v>
+        <v>6841463</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119820554</v>
+        <v>119820555</v>
       </c>
       <c r="B5" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,13 +1052,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486159</v>
+        <v>486170</v>
       </c>
       <c r="R5" t="n">
-        <v>6841747</v>
+        <v>6841676</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119820559</v>
+        <v>119820554</v>
       </c>
       <c r="B6" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486391</v>
+        <v>486159</v>
       </c>
       <c r="R6" t="n">
-        <v>6841482</v>
+        <v>6841747</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119820555</v>
+        <v>119820559</v>
       </c>
       <c r="B7" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,13 +1274,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486170</v>
+        <v>486391</v>
       </c>
       <c r="R7" t="n">
-        <v>6841676</v>
+        <v>6841482</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119820560</v>
+        <v>119820557</v>
       </c>
       <c r="B8" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486399</v>
+        <v>486203</v>
       </c>
       <c r="R8" t="n">
-        <v>6841463</v>
+        <v>6841583</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>

--- a/artfynd/A 52294-2020 artfynd.xlsx
+++ b/artfynd/A 52294-2020 artfynd.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119820556</v>
+        <v>119820557</v>
       </c>
       <c r="B3" t="n">
         <v>97930</v>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486186</v>
+        <v>486203</v>
       </c>
       <c r="R3" t="n">
-        <v>6841640</v>
+        <v>6841583</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119820560</v>
+        <v>119820554</v>
       </c>
       <c r="B4" t="n">
         <v>97930</v>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486399</v>
+        <v>486159</v>
       </c>
       <c r="R4" t="n">
-        <v>6841463</v>
+        <v>6841747</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1119,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119820554</v>
+        <v>119820556</v>
       </c>
       <c r="B6" t="n">
         <v>97930</v>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486159</v>
+        <v>486186</v>
       </c>
       <c r="R6" t="n">
-        <v>6841747</v>
+        <v>6841640</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1341,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119820557</v>
+        <v>119820560</v>
       </c>
       <c r="B8" t="n">
         <v>97930</v>
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486203</v>
+        <v>486399</v>
       </c>
       <c r="R8" t="n">
-        <v>6841583</v>
+        <v>6841463</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>

--- a/artfynd/A 52294-2020 artfynd.xlsx
+++ b/artfynd/A 52294-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119820552</v>
+        <v>119820556</v>
       </c>
       <c r="B2" t="n">
         <v>97930</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>486239</v>
+        <v>486186</v>
       </c>
       <c r="R2" t="n">
-        <v>6841652</v>
+        <v>6841640</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119820554</v>
+        <v>119820560</v>
       </c>
       <c r="B4" t="n">
         <v>97930</v>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486159</v>
+        <v>486399</v>
       </c>
       <c r="R4" t="n">
-        <v>6841747</v>
+        <v>6841463</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119820555</v>
+        <v>119820559</v>
       </c>
       <c r="B5" t="n">
         <v>97930</v>
@@ -1052,13 +1052,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486170</v>
+        <v>486391</v>
       </c>
       <c r="R5" t="n">
-        <v>6841676</v>
+        <v>6841482</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119820556</v>
+        <v>119820552</v>
       </c>
       <c r="B6" t="n">
         <v>97930</v>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486186</v>
+        <v>486239</v>
       </c>
       <c r="R6" t="n">
-        <v>6841640</v>
+        <v>6841652</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119820559</v>
+        <v>119820555</v>
       </c>
       <c r="B7" t="n">
         <v>97930</v>
@@ -1274,13 +1274,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486391</v>
+        <v>486170</v>
       </c>
       <c r="R7" t="n">
-        <v>6841482</v>
+        <v>6841676</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119820560</v>
+        <v>119820554</v>
       </c>
       <c r="B8" t="n">
         <v>97930</v>
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486399</v>
+        <v>486159</v>
       </c>
       <c r="R8" t="n">
-        <v>6841463</v>
+        <v>6841747</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
